--- a/ML-Current/polystyrene-imputated-molecular-descriptor-includes-inj-volume-2-15-25.xlsx
+++ b/ML-Current/polystyrene-imputated-molecular-descriptor-includes-inj-volume-2-15-25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dillo\OneDrive\Documents\GitHub\LCCC-ML\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aced77f8e52479c3/Documents/GitHub/Dr.Wang_pr/ML-Current/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79345E75-5576-4679-BF90-8B8A326A5261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1695" yWindow="3368" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -977,135 +977,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:FT173"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.265625" bestFit="1" customWidth="1"/>
     <col min="21" max="32" width="12" bestFit="1" customWidth="1"/>
-    <col min="33" max="41" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="41" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.3984375" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="17" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="21.265625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.1328125" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="51" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.73046875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="22.1328125" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="68" max="76" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="77" max="79" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="81" max="87" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="24.1328125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="29.265625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="30.3984375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="68" max="76" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="77" max="79" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="81" max="87" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="16.1328125" bestFit="1" customWidth="1"/>
     <col min="89" max="95" width="16" bestFit="1" customWidth="1"/>
     <col min="96" max="96" width="17" bestFit="1" customWidth="1"/>
     <col min="97" max="97" width="10" bestFit="1" customWidth="1"/>
-    <col min="98" max="106" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="98" max="106" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="110" max="110" width="19" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="122" max="122" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="123" max="123" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="132" max="132" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="136" max="136" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="18.73046875" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="15.86328125" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="20.1328125" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="23.265625" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="24.59765625" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="19.86328125" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="29.73046875" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="24.73046875" bestFit="1" customWidth="1"/>
     <col min="138" max="138" width="38" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="140" max="140" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="146" max="146" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="147" max="147" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="148" max="148" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="150" max="150" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="151" max="151" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="152" max="152" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="36.73046875" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="32.73046875" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="38.59765625" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="33.86328125" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="31.59765625" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="33.1328125" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="33.265625" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="34.59765625" bestFit="1" customWidth="1"/>
+    <col min="147" max="147" width="29.3984375" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="31.59765625" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="29.86328125" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="38.59765625" bestFit="1" customWidth="1"/>
+    <col min="151" max="151" width="33.1328125" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="33.73046875" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="36.73046875" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="34.3984375" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="32.1328125" bestFit="1" customWidth="1"/>
     <col min="156" max="156" width="37" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="158" max="158" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="159" max="159" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="160" max="160" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="163" max="163" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="164" max="164" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="165" max="165" width="47.85546875" bestFit="1" customWidth="1"/>
-    <col min="166" max="166" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="168" max="168" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="46.73046875" bestFit="1" customWidth="1"/>
+    <col min="158" max="158" width="33.3984375" bestFit="1" customWidth="1"/>
+    <col min="159" max="159" width="30.86328125" bestFit="1" customWidth="1"/>
+    <col min="160" max="160" width="23.1328125" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="30.73046875" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="27.3984375" bestFit="1" customWidth="1"/>
+    <col min="163" max="163" width="32.3984375" bestFit="1" customWidth="1"/>
+    <col min="164" max="164" width="34.59765625" bestFit="1" customWidth="1"/>
+    <col min="165" max="165" width="47.86328125" bestFit="1" customWidth="1"/>
+    <col min="166" max="166" width="39.86328125" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="168" max="168" width="32.1328125" bestFit="1" customWidth="1"/>
     <col min="169" max="169" width="36" bestFit="1" customWidth="1"/>
-    <col min="170" max="170" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="171" max="171" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="172" max="172" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="170" max="170" width="32.86328125" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="25.73046875" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="23.59765625" bestFit="1" customWidth="1"/>
     <col min="173" max="173" width="35" bestFit="1" customWidth="1"/>
     <col min="174" max="174" width="47" bestFit="1" customWidth="1"/>
     <col min="175" max="175" width="40" bestFit="1" customWidth="1"/>
-    <col min="176" max="176" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="176" max="176" width="19.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>10</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>9</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>9</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>9</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>9</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>7</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>7</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>7</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>7</v>
       </c>
@@ -7995,7 +7995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>7</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>9</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>9</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>8</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>8</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>10</v>
       </c>
@@ -11175,7 +11175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>8</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>9</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>7</v>
       </c>
@@ -12765,7 +12765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>7</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>7</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>7</v>
       </c>
@@ -14355,7 +14355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>7</v>
       </c>
@@ -14885,7 +14885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>10</v>
       </c>
@@ -15415,7 +15415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>7</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>8</v>
       </c>
@@ -16475,7 +16475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>10</v>
       </c>
@@ -17005,7 +17005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>9</v>
       </c>
@@ -17535,7 +17535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>9</v>
       </c>
@@ -18065,7 +18065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>9</v>
       </c>
@@ -18595,7 +18595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>9</v>
       </c>
@@ -19125,7 +19125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>9</v>
       </c>
@@ -19655,7 +19655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>9</v>
       </c>
@@ -20185,7 +20185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>9</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>9</v>
       </c>
@@ -21245,7 +21245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>9</v>
       </c>
@@ -21775,7 +21775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>9</v>
       </c>
@@ -22305,7 +22305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>9</v>
       </c>
@@ -22835,7 +22835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>8</v>
       </c>
@@ -23365,7 +23365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>8</v>
       </c>
@@ -23895,7 +23895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>8</v>
       </c>
@@ -24425,7 +24425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>7</v>
       </c>
@@ -24955,7 +24955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>7</v>
       </c>
@@ -25485,7 +25485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>8</v>
       </c>
@@ -26015,7 +26015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>8</v>
       </c>
@@ -26545,7 +26545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>8</v>
       </c>
@@ -27075,7 +27075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>9</v>
       </c>
@@ -27605,7 +27605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>9</v>
       </c>
@@ -28135,7 +28135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>10</v>
       </c>
@@ -28665,7 +28665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>10</v>
       </c>
@@ -29195,7 +29195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>9</v>
       </c>
@@ -29725,7 +29725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>7</v>
       </c>
@@ -30255,7 +30255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>10</v>
       </c>
@@ -30785,7 +30785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>7</v>
       </c>
@@ -31315,7 +31315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>7</v>
       </c>
@@ -31845,7 +31845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>7</v>
       </c>
@@ -32375,7 +32375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>8</v>
       </c>
@@ -32905,7 +32905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>8</v>
       </c>
@@ -33435,7 +33435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>8</v>
       </c>
@@ -33965,7 +33965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>6</v>
       </c>
@@ -34495,7 +34495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>8</v>
       </c>
@@ -35025,7 +35025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>8</v>
       </c>
@@ -35555,7 +35555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>8</v>
       </c>
@@ -36085,7 +36085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>8</v>
       </c>
@@ -36615,7 +36615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>9</v>
       </c>
@@ -37145,7 +37145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>9</v>
       </c>
@@ -37675,7 +37675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>6</v>
       </c>
@@ -38205,7 +38205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>7</v>
       </c>
@@ -38735,7 +38735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>7</v>
       </c>
@@ -39265,7 +39265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>7</v>
       </c>
@@ -39795,7 +39795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>7</v>
       </c>
@@ -40325,7 +40325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>6</v>
       </c>
@@ -40855,7 +40855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>6</v>
       </c>
@@ -41385,7 +41385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>7</v>
       </c>
@@ -41915,7 +41915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>7</v>
       </c>
@@ -42445,7 +42445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>6</v>
       </c>
@@ -42975,7 +42975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>9</v>
       </c>
@@ -43505,7 +43505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>9</v>
       </c>
@@ -44035,7 +44035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>5</v>
       </c>
@@ -44565,7 +44565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>8</v>
       </c>
@@ -45095,7 +45095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>8</v>
       </c>
@@ -45625,7 +45625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>8</v>
       </c>
@@ -46155,7 +46155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>8</v>
       </c>
@@ -46685,7 +46685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>8</v>
       </c>
@@ -47215,7 +47215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>8</v>
       </c>
@@ -47745,7 +47745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>8</v>
       </c>
@@ -48275,7 +48275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>8</v>
       </c>
@@ -48805,7 +48805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>7</v>
       </c>
@@ -49335,7 +49335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>10</v>
       </c>
@@ -49865,7 +49865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>8</v>
       </c>
@@ -50395,7 +50395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>8</v>
       </c>
@@ -50925,7 +50925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>6</v>
       </c>
@@ -51455,7 +51455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>9</v>
       </c>
@@ -51985,7 +51985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>8</v>
       </c>
@@ -52515,7 +52515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>10</v>
       </c>
@@ -53045,7 +53045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>7</v>
       </c>
@@ -53575,7 +53575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>7</v>
       </c>
@@ -54105,7 +54105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>9</v>
       </c>
@@ -54635,7 +54635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>6</v>
       </c>
@@ -55165,7 +55165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>10</v>
       </c>
@@ -55695,7 +55695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>8</v>
       </c>
@@ -56225,7 +56225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>6</v>
       </c>
@@ -56755,7 +56755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>6</v>
       </c>
@@ -57285,7 +57285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>9</v>
       </c>
@@ -57815,7 +57815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>9</v>
       </c>
@@ -58345,7 +58345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>9</v>
       </c>
@@ -58875,7 +58875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>9</v>
       </c>
@@ -59405,7 +59405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>8</v>
       </c>
@@ -59935,7 +59935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>10</v>
       </c>
@@ -60465,7 +60465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>10</v>
       </c>
@@ -60995,7 +60995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>10</v>
       </c>
@@ -61525,7 +61525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>9</v>
       </c>
@@ -62055,7 +62055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>9</v>
       </c>
@@ -62585,7 +62585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>9</v>
       </c>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>9</v>
       </c>
@@ -63645,7 +63645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>9</v>
       </c>
@@ -64175,7 +64175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>9</v>
       </c>
@@ -64705,7 +64705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>6</v>
       </c>
@@ -65235,7 +65235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>8</v>
       </c>
@@ -65765,7 +65765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>6</v>
       </c>
@@ -66295,7 +66295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>9</v>
       </c>
@@ -66825,7 +66825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>9</v>
       </c>
@@ -67355,7 +67355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>9</v>
       </c>
@@ -67885,7 +67885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>9</v>
       </c>
@@ -68415,7 +68415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>9</v>
       </c>
@@ -68945,7 +68945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>9</v>
       </c>
@@ -69475,7 +69475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>8</v>
       </c>
@@ -70005,7 +70005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>8</v>
       </c>
@@ -70535,7 +70535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>8</v>
       </c>
@@ -71065,7 +71065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>5</v>
       </c>
@@ -71595,7 +71595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>6</v>
       </c>
@@ -72125,7 +72125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>6</v>
       </c>
@@ -72655,7 +72655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>9</v>
       </c>
@@ -73185,7 +73185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>9</v>
       </c>
@@ -73715,7 +73715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>9</v>
       </c>
@@ -74245,7 +74245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>8</v>
       </c>
@@ -74775,7 +74775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>9</v>
       </c>
@@ -75305,7 +75305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>10</v>
       </c>
@@ -75835,7 +75835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>10</v>
       </c>
@@ -76365,7 +76365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>9</v>
       </c>
@@ -76895,7 +76895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>10</v>
       </c>
@@ -77425,7 +77425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>10</v>
       </c>
@@ -77955,7 +77955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>10</v>
       </c>
@@ -78485,7 +78485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>9</v>
       </c>
@@ -79015,7 +79015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>10</v>
       </c>
@@ -79545,7 +79545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>10</v>
       </c>
@@ -80075,7 +80075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>10</v>
       </c>
@@ -80605,7 +80605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>8</v>
       </c>
@@ -81135,7 +81135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>9</v>
       </c>
@@ -81665,7 +81665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>8</v>
       </c>
@@ -82195,7 +82195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>8</v>
       </c>
@@ -82725,7 +82725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>9</v>
       </c>
@@ -83255,7 +83255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>9</v>
       </c>
@@ -83785,7 +83785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>10</v>
       </c>
@@ -84315,7 +84315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>10</v>
       </c>
@@ -84845,7 +84845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>9</v>
       </c>
@@ -85375,7 +85375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>10</v>
       </c>
@@ -85905,7 +85905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>10</v>
       </c>
@@ -86435,7 +86435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>8</v>
       </c>
@@ -86965,7 +86965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>8</v>
       </c>
@@ -87495,7 +87495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>8</v>
       </c>
@@ -88025,7 +88025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>10</v>
       </c>
@@ -88555,7 +88555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>10</v>
       </c>
@@ -89085,7 +89085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>10</v>
       </c>
@@ -89615,7 +89615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>10</v>
       </c>
@@ -90145,7 +90145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>9</v>
       </c>
@@ -90675,7 +90675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>10</v>
       </c>
@@ -91205,7 +91205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>10</v>
       </c>
@@ -91735,7 +91735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>10</v>
       </c>
@@ -92265,7 +92265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:176" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>10</v>
       </c>
